--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Clase-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,09</t>
+          <t>1,56; 5,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,36</t>
+          <t>2,39; 5,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,97</t>
+          <t>2,03; 7,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,02</t>
+          <t>2,68; 7,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,37</t>
+          <t>6,78; 11,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,1</t>
+          <t>1,04; 3,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,37</t>
+          <t>2,5; 5,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,42</t>
+          <t>4,89; 7,45</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,65</t>
+          <t>0,96; 3,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,26</t>
+          <t>0,52; 3,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,4</t>
+          <t>2,9; 6,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,34</t>
+          <t>2,56; 7,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,71</t>
+          <t>1,41; 5,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 14,07</t>
+          <t>8,7; 13,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,67</t>
+          <t>1,92; 4,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,71</t>
+          <t>1,32; 3,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,32</t>
+          <t>6,38; 9,27</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,65</t>
+          <t>3,04; 6,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,19</t>
+          <t>1,32; 4,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,01</t>
+          <t>2,11; 10,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,65</t>
+          <t>3,81; 9,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 21,48</t>
+          <t>9,36; 21,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 23,22</t>
+          <t>13,85; 23,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,89</t>
+          <t>3,79; 6,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,31</t>
+          <t>3,91; 7,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,49</t>
+          <t>3,55; 12,4</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,03</t>
+          <t>4,23; 7,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,61</t>
+          <t>2,5; 4,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,67</t>
+          <t>8,25; 11,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,88</t>
+          <t>4,31; 7,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,06</t>
+          <t>4,59; 8,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,63</t>
+          <t>4,71; 11,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,94</t>
+          <t>4,59; 6,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,67</t>
+          <t>3,72; 5,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 10,67</t>
+          <t>6,25; 10,69</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,58</t>
+          <t>2,06; 5,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,73</t>
+          <t>3,9; 7,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,88</t>
+          <t>6,73; 11,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,27; 15,25</t>
+          <t>10,38; 15,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,88</t>
+          <t>9,7; 14,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,26; 24,66</t>
+          <t>16,25; 24,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 10,69</t>
+          <t>7,49; 10,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 10,94</t>
+          <t>7,68; 10,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,92; 19,17</t>
+          <t>13,84; 19,02</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,4</t>
+          <t>0,6; 3,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,22; 15,35</t>
+          <t>10,85; 15,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,74</t>
+          <t>9,4; 13,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,11; 19,45</t>
+          <t>15,23; 19,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,92; 12,49</t>
+          <t>9,13; 12,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 11,06</t>
+          <t>7,67; 10,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,85; 15,3</t>
+          <t>11,95; 15,37</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,27</t>
+          <t>2,96; 4,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,76</t>
+          <t>2,57; 3,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,6</t>
+          <t>5,16; 7,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,35; 10,39</t>
+          <t>8,23; 10,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 10,0</t>
+          <t>8,05; 10,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,35; 15,48</t>
+          <t>11,62; 15,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,92; 7,22</t>
+          <t>5,83; 7,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,7</t>
+          <t>5,5; 6,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,18; 11,44</t>
+          <t>9,2; 11,34</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5309</t>
+          <t>0; 5953</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6439; 21854</t>
+          <t>6677; 22289</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11952; 27061</t>
+          <t>12055; 27320</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7125; 21913</t>
+          <t>6387; 23109</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8602; 24351</t>
+          <t>9296; 26161</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30085; 50872</t>
+          <t>30318; 49494</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7578; 23274</t>
+          <t>7817; 23721</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19034; 41673</t>
+          <t>19411; 41600</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285; 70678</t>
+          <t>46620; 70994</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3950; 15281</t>
+          <t>4026; 15593</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1918; 12288</t>
+          <t>1957; 12552</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13329; 28955</t>
+          <t>13121; 28911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7692; 24794</t>
+          <t>8646; 24985</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5806; 21245</t>
+          <t>5242; 20680</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33669; 53811</t>
+          <t>33293; 53139</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14800; 35352</t>
+          <t>14564; 34711</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9488; 27835</t>
+          <t>9893; 27954</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51637; 77841</t>
+          <t>53239; 77347</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18811; 41886</t>
+          <t>19145; 42816</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6896; 21854</t>
+          <t>6892; 21641</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14159; 66864</t>
+          <t>14120; 68330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9629; 25096</t>
+          <t>9912; 25828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15712; 35691</t>
+          <t>15553; 35737</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23813; 38753</t>
+          <t>23121; 38938</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33835; 61254</t>
+          <t>33758; 60248</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26425; 50312</t>
+          <t>26882; 51974</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30937; 104324</t>
+          <t>29680; 103547</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49762; 81525</t>
+          <t>48987; 81865</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28733; 53037</t>
+          <t>28726; 53848</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85623; 120803</t>
+          <t>85391; 119446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32707; 60399</t>
+          <t>33076; 60285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38516; 66526</t>
+          <t>37914; 67131</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41531; 113751</t>
+          <t>46053; 112540</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90045; 133609</t>
+          <t>88431; 131547</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72360; 112053</t>
+          <t>73468; 110688</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131721; 214683</t>
+          <t>125804; 215155</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11615; 28494</t>
+          <t>10532; 27811</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24423; 47981</t>
+          <t>24238; 45476</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33376; 56457</t>
+          <t>31983; 55631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78185; 116148</t>
+          <t>79017; 118684</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>72457; 109839</t>
+          <t>71614; 108328</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>128399; 207477</t>
+          <t>136699; 210075</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94561; 135966</t>
+          <t>95227; 136900</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>103941; 148723</t>
+          <t>104313; 146198</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>183293; 252399</t>
+          <t>182212; 250407</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6302</t>
+          <t>0; 7826</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5700</t>
+          <t>0; 6431</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1625; 8174</t>
+          <t>1435; 8561</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>124442; 170260</t>
+          <t>120365; 169680</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>102925; 148630</t>
+          <t>101711; 147503</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>115013; 148077</t>
+          <t>115970; 147630</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>122725; 171930</t>
+          <t>125626; 170994</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>104882; 151497</t>
+          <t>105080; 147476</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>118740; 153296</t>
+          <t>119699; 153984</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>99698; 146012</t>
+          <t>101221; 147631</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>87491; 127310</t>
+          <t>87037; 125343</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>178452; 256450</t>
+          <t>174142; 259342</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>296300; 368916</t>
+          <t>292109; 367271</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>281043; 353168</t>
+          <t>284270; 358850</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>405995; 553937</t>
+          <t>415797; 556967</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>412578; 503049</t>
+          <t>406276; 493248</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>381264; 463498</t>
+          <t>380574; 466870</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>638292; 795602</t>
+          <t>640071; 788847</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Clase-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,19</t>
+          <t>1,46; 5,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,41</t>
+          <t>2,55; 5,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,35</t>
+          <t>1,94; 6,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,54</t>
+          <t>2,52; 7,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 11,06</t>
+          <t>6,81; 11,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,16</t>
+          <t>0,97; 3,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,36</t>
+          <t>2,54; 5,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,45</t>
+          <t>4,96; 7,46</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,72</t>
+          <t>0,95; 3,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,33</t>
+          <t>0,51; 3,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,39</t>
+          <t>2,89; 6,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,39</t>
+          <t>2,56; 7,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,56</t>
+          <t>1,46; 5,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 13,89</t>
+          <t>9,05; 13,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,59</t>
+          <t>1,87; 4,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,73</t>
+          <t>1,29; 3,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,27</t>
+          <t>6,16; 9,29</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,8</t>
+          <t>2,97; 6,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,15</t>
+          <t>1,4; 4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 10,23</t>
+          <t>6,61; 11,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,93</t>
+          <t>3,69; 10,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 21,51</t>
+          <t>9,37; 21,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 23,33</t>
+          <t>13,93; 23,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,77</t>
+          <t>3,81; 6,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,55</t>
+          <t>3,74; 7,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 12,4</t>
+          <t>9,36; 13,9</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,06</t>
+          <t>4,35; 7,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,68</t>
+          <t>2,49; 4,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,54</t>
+          <t>7,93; 11,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,86</t>
+          <t>4,33; 8,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,13</t>
+          <t>4,62; 7,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,51</t>
+          <t>9,34; 12,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,83</t>
+          <t>4,63; 6,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 5,6</t>
+          <t>3,61; 5,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,69</t>
+          <t>8,93; 11,3</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,45</t>
+          <t>2,08; 5,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,33</t>
+          <t>4,07; 7,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,73; 11,71</t>
+          <t>6,18; 10,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 15,59</t>
+          <t>10,44; 15,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,7; 14,67</t>
+          <t>9,61; 14,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 24,97</t>
+          <t>20,72; 25,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,76</t>
+          <t>7,55; 10,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 10,76</t>
+          <t>7,6; 10,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,84; 19,02</t>
+          <t>15,33; 18,63</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,56</t>
+          <t>0,58; 3,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,85; 15,3</t>
+          <t>11,12; 15,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,4; 13,63</t>
+          <t>9,66; 13,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,23; 19,39</t>
+          <t>15,02; 18,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,13; 12,42</t>
+          <t>8,96; 12,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,77</t>
+          <t>7,74; 11,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,95; 15,37</t>
+          <t>11,72; 15,23</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,31</t>
+          <t>2,96; 4,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,7</t>
+          <t>2,61; 3,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,68</t>
+          <t>6,18; 7,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 10,35</t>
+          <t>8,37; 10,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,05; 10,16</t>
+          <t>7,93; 10,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,62; 15,57</t>
+          <t>14,19; 16,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,07</t>
+          <t>5,87; 7,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 6,75</t>
+          <t>5,53; 6,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 11,34</t>
+          <t>10,56; 11,85</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>42404</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56966</t>
+          <t>63705</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5953</t>
+          <t>0; 5260</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6677; 22289</t>
+          <t>6266; 21658</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12055; 27320</t>
+          <t>14047; 31285</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6387; 23109</t>
+          <t>6092; 21221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9296; 26161</t>
+          <t>8737; 25954</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30318; 49494</t>
+          <t>33255; 54133</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7817; 23721</t>
+          <t>7267; 23898</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19411; 41600</t>
+          <t>19725; 41932</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46620; 70994</t>
+          <t>51568; 77475</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43223</t>
+          <t>47752</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>68866</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4026; 15593</t>
+          <t>3977; 15837</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1957; 12552</t>
+          <t>1933; 12289</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13121; 28911</t>
+          <t>13988; 30293</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8646; 24985</t>
+          <t>8637; 24477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5242; 20680</t>
+          <t>5440; 20404</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33293; 53139</t>
+          <t>38297; 59030</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14564; 34711</t>
+          <t>14117; 34902</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9893; 27954</t>
+          <t>9646; 27884</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53239; 77347</t>
+          <t>55872; 84193</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30390</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69479</t>
+          <t>75457</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19145; 42816</t>
+          <t>18668; 41968</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6892; 21641</t>
+          <t>7330; 22490</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14120; 68330</t>
+          <t>31190; 54251</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9912; 25828</t>
+          <t>9604; 26138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15553; 35737</t>
+          <t>15568; 35239</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23121; 38938</t>
+          <t>26115; 43275</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33758; 60248</t>
+          <t>33909; 61574</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26882; 51974</t>
+          <t>25764; 52044</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29680; 103547</t>
+          <t>61678; 91611</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100372</t>
+          <t>106086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84395</t>
+          <t>93789</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>184767</t>
+          <t>199875</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48987; 81865</t>
+          <t>50399; 82739</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28726; 53848</t>
+          <t>28669; 53082</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85391; 119446</t>
+          <t>89715; 125876</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33076; 60285</t>
+          <t>33211; 62538</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37914; 67131</t>
+          <t>38137; 65007</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46053; 112540</t>
+          <t>80464; 109738</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88431; 131547</t>
+          <t>89155; 133179</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73468; 110688</t>
+          <t>71411; 109503</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125804; 215155</t>
+          <t>178009; 225314</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43654</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>178488</t>
+          <t>190189</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>222141</t>
+          <t>236207</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10532; 27811</t>
+          <t>10616; 28217</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24238; 45476</t>
+          <t>25288; 46444</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31983; 55631</t>
+          <t>35076; 58579</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79017; 118684</t>
+          <t>79515; 115549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>71614; 108328</t>
+          <t>70976; 106939</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>136699; 210075</t>
+          <t>172176; 209803</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95227; 136900</t>
+          <t>96073; 137256</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>104313; 146198</t>
+          <t>103322; 146330</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182212; 250407</t>
+          <t>214376; 260534</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>131226</t>
+          <t>141881</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>134936</t>
+          <t>145608</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 7826</t>
+          <t>0; 6055</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6431</t>
+          <t>0; 5693</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1435; 8561</t>
+          <t>1369; 8058</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120365; 169680</t>
+          <t>123367; 171330</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>101711; 147503</t>
+          <t>104512; 148127</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>115970; 147630</t>
+          <t>126782; 160207</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>125626; 170994</t>
+          <t>123295; 169674</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>105080; 147476</t>
+          <t>106030; 152135</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>119699; 153984</t>
+          <t>126758; 164747</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225586</t>
+          <t>240032</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>506182</t>
+          <t>549685</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>731769</t>
+          <t>789717</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>101221; 147631</t>
+          <t>101278; 146210</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>87037; 125343</t>
+          <t>88498; 130367</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174142; 259342</t>
+          <t>212587; 270593</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292109; 367271</t>
+          <t>297154; 368601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>284270; 358850</t>
+          <t>279945; 355873</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>415797; 556967</t>
+          <t>515779; 585174</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>406276; 493248</t>
+          <t>409268; 496019</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>380574; 466870</t>
+          <t>382840; 463680</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>640071; 788847</t>
+          <t>747410; 838922</t>
         </is>
       </c>
     </row>
